--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T14:37:20+00:00</t>
+    <t>2026-09-07T15:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:18:54+00:00</t>
+    <t>2026-09-07T18:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:27:01+00:00</t>
+    <t>2026-09-07T18:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:38:14+00:00</t>
+    <t>2026-09-08T08:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:42:22+00:00</t>
+    <t>2026-09-08T08:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:49:15+00:00</t>
+    <t>2026-09-08T09:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:59:59+00:00</t>
+    <t>2026-09-08T14:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>This material includes SNOMED Clinical Terms® (SNOMED CT®) which is used by permission of SNOMED International. All rights reserved. SNOMED CT®, was originally created by The College of American Pathologists. SNOMED and SNOMED CT are registered trademarks of SNOMED International. Implementers of these artefacts must have the appropriate SNOMED CT Affiliate license.</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -364,14 +367,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -393,7 +398,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -401,29 +406,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:28:13+00:00</t>
+    <t>2026-09-08T14:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:35:38+00:00</t>
+    <t>2026-09-08T14:50:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:50:12+00:00</t>
+    <t>2026-09-08T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:07:59+00:00</t>
+    <t>2026-09-08T15:32:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:32:50+00:00</t>
+    <t>2026-09-08T17:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:49:28+00:00</t>
+    <t>2026-09-08T19:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T19:41:07+00:00</t>
+    <t>2026-09-12T21:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T21:08:11+00:00</t>
+    <t>2026-09-12T22:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T22:28:47+00:00</t>
+    <t>2026-09-12T22:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
